--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1142,14 +1142,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132421585</v>
+        <v>132421654</v>
       </c>
       <c r="B6" t="n">
         <v>56811</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691726</v>
+        <v>691723</v>
       </c>
       <c r="R6" t="n">
-        <v>6600487</v>
+        <v>6600486</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1258,14 +1258,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132421654</v>
+        <v>132421646</v>
       </c>
       <c r="B7" t="n">
         <v>56811</v>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691723</v>
+        <v>691724</v>
       </c>
       <c r="R7" t="n">
         <v>6600486</v>
@@ -1374,14 +1374,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132421646</v>
+        <v>132421585</v>
       </c>
       <c r="B8" t="n">
         <v>56811</v>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691724</v>
+        <v>691726</v>
       </c>
       <c r="R8" t="n">
-        <v>6600486</v>
+        <v>6600487</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1845,7 +1845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132421615</v>
+        <v>132421652</v>
       </c>
       <c r="B12" t="n">
         <v>56811</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691729</v>
+        <v>691724</v>
       </c>
       <c r="R12" t="n">
-        <v>6600482</v>
+        <v>6600483</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1954,39 +1954,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132421599</v>
+        <v>132421705</v>
       </c>
       <c r="B13" t="n">
-        <v>56811</v>
+        <v>56830</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691727</v>
+        <v>691725</v>
       </c>
       <c r="R13" t="n">
-        <v>6600487</v>
+        <v>6600486</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2077,7 +2077,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132421652</v>
+        <v>132421615</v>
       </c>
       <c r="B14" t="n">
         <v>56811</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691724</v>
+        <v>691729</v>
       </c>
       <c r="R14" t="n">
-        <v>6600483</v>
+        <v>6600482</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2186,14 +2186,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132421617</v>
+        <v>132421599</v>
       </c>
       <c r="B15" t="n">
         <v>56811</v>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691729</v>
+        <v>691727</v>
       </c>
       <c r="R15" t="n">
-        <v>6600481</v>
+        <v>6600487</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2302,39 +2302,39 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132421705</v>
+        <v>132421617</v>
       </c>
       <c r="B16" t="n">
-        <v>56830</v>
+        <v>56811</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691725</v>
+        <v>691729</v>
       </c>
       <c r="R16" t="n">
-        <v>6600486</v>
+        <v>6600481</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2388,12 +2388,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2418,39 +2418,39 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132421589</v>
+        <v>132421540</v>
       </c>
       <c r="B17" t="n">
-        <v>56811</v>
+        <v>56825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691725</v>
+        <v>691726</v>
       </c>
       <c r="R17" t="n">
-        <v>6600486</v>
+        <v>6600484</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2773,32 +2773,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132421540</v>
+        <v>132421589</v>
       </c>
       <c r="B20" t="n">
-        <v>56825</v>
+        <v>56811</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691726</v>
+        <v>691725</v>
       </c>
       <c r="R20" t="n">
-        <v>6600484</v>
+        <v>6600486</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2998,14 +2998,14 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132421604</v>
+        <v>132421688</v>
       </c>
       <c r="B22" t="n">
         <v>56811</v>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691727</v>
+        <v>691717</v>
       </c>
       <c r="R22" t="n">
-        <v>6600488</v>
+        <v>6600486</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132421673</v>
+        <v>132421604</v>
       </c>
       <c r="B23" t="n">
         <v>56811</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691729</v>
+        <v>691727</v>
       </c>
       <c r="R23" t="n">
         <v>6600488</v>
@@ -3230,14 +3230,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132421688</v>
+        <v>132421673</v>
       </c>
       <c r="B24" t="n">
         <v>56811</v>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691717</v>
+        <v>691729</v>
       </c>
       <c r="R24" t="n">
-        <v>6600486</v>
+        <v>6600488</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132421614</v>
+        <v>132421686</v>
       </c>
       <c r="B25" t="n">
         <v>56811</v>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691728</v>
+        <v>691710</v>
       </c>
       <c r="R25" t="n">
-        <v>6600482</v>
+        <v>6600483</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132421686</v>
+        <v>132421614</v>
       </c>
       <c r="B26" t="n">
         <v>56811</v>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691710</v>
+        <v>691728</v>
       </c>
       <c r="R26" t="n">
-        <v>6600483</v>
+        <v>6600482</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3578,14 +3578,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132421613</v>
+        <v>132421388</v>
       </c>
       <c r="B27" t="n">
         <v>56811</v>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691728</v>
+        <v>691727</v>
       </c>
       <c r="R27" t="n">
-        <v>6600483</v>
+        <v>6600493</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3701,7 +3701,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132421388</v>
+        <v>132421613</v>
       </c>
       <c r="B28" t="n">
         <v>56811</v>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691727</v>
+        <v>691728</v>
       </c>
       <c r="R28" t="n">
-        <v>6600493</v>
+        <v>6600483</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3933,7 +3933,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132421404</v>
+        <v>132421656</v>
       </c>
       <c r="B30" t="n">
         <v>56811</v>
@@ -3985,7 +3985,7 @@
         <v>691723</v>
       </c>
       <c r="R30" t="n">
-        <v>6600494</v>
+        <v>6600487</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4049,7 +4049,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132421656</v>
+        <v>132421404</v>
       </c>
       <c r="B31" t="n">
         <v>56811</v>
@@ -4101,7 +4101,7 @@
         <v>691723</v>
       </c>
       <c r="R31" t="n">
-        <v>6600487</v>
+        <v>6600494</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -3933,7 +3933,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132421656</v>
+        <v>132421404</v>
       </c>
       <c r="B30" t="n">
         <v>56811</v>
@@ -3985,7 +3985,7 @@
         <v>691723</v>
       </c>
       <c r="R30" t="n">
-        <v>6600487</v>
+        <v>6600494</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4049,7 +4049,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132421404</v>
+        <v>132421656</v>
       </c>
       <c r="B31" t="n">
         <v>56811</v>
@@ -4101,7 +4101,7 @@
         <v>691723</v>
       </c>
       <c r="R31" t="n">
-        <v>6600494</v>
+        <v>6600487</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -3933,7 +3933,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132421404</v>
+        <v>132421656</v>
       </c>
       <c r="B30" t="n">
         <v>56811</v>
@@ -3985,7 +3985,7 @@
         <v>691723</v>
       </c>
       <c r="R30" t="n">
-        <v>6600494</v>
+        <v>6600487</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4049,7 +4049,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132421656</v>
+        <v>132421404</v>
       </c>
       <c r="B31" t="n">
         <v>56811</v>
@@ -4101,7 +4101,7 @@
         <v>691723</v>
       </c>
       <c r="R31" t="n">
-        <v>6600487</v>
+        <v>6600494</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132421821</v>
+        <v>132421630</v>
       </c>
       <c r="B3" t="n">
         <v>56811</v>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691718</v>
+        <v>691727</v>
       </c>
       <c r="R3" t="n">
-        <v>6600485</v>
+        <v>6600486</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,12 +880,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132421630</v>
+        <v>132421821</v>
       </c>
       <c r="B4" t="n">
         <v>56811</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691727</v>
+        <v>691718</v>
       </c>
       <c r="R4" t="n">
-        <v>6600486</v>
+        <v>6600485</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,12 +996,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1142,14 +1142,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132421654</v>
+        <v>132421572</v>
       </c>
       <c r="B6" t="n">
         <v>56811</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691723</v>
+        <v>691728</v>
       </c>
       <c r="R6" t="n">
-        <v>6600486</v>
+        <v>6600492</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1258,14 +1258,14 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132421646</v>
+        <v>132421585</v>
       </c>
       <c r="B7" t="n">
         <v>56811</v>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691724</v>
+        <v>691726</v>
       </c>
       <c r="R7" t="n">
-        <v>6600486</v>
+        <v>6600487</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1374,14 +1374,14 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132421585</v>
+        <v>132421654</v>
       </c>
       <c r="B8" t="n">
         <v>56811</v>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691726</v>
+        <v>691723</v>
       </c>
       <c r="R8" t="n">
-        <v>6600487</v>
+        <v>6600486</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1497,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132421572</v>
+        <v>132421646</v>
       </c>
       <c r="B9" t="n">
         <v>56811</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691728</v>
+        <v>691724</v>
       </c>
       <c r="R9" t="n">
-        <v>6600492</v>
+        <v>6600486</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1845,7 +1845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132421652</v>
+        <v>132421615</v>
       </c>
       <c r="B12" t="n">
         <v>56811</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691724</v>
+        <v>691729</v>
       </c>
       <c r="R12" t="n">
-        <v>6600483</v>
+        <v>6600482</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1954,39 +1954,39 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132421705</v>
+        <v>132421599</v>
       </c>
       <c r="B13" t="n">
-        <v>56830</v>
+        <v>56811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691725</v>
+        <v>691727</v>
       </c>
       <c r="R13" t="n">
-        <v>6600486</v>
+        <v>6600487</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2077,7 +2077,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132421615</v>
+        <v>132421652</v>
       </c>
       <c r="B14" t="n">
         <v>56811</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691729</v>
+        <v>691724</v>
       </c>
       <c r="R14" t="n">
-        <v>6600482</v>
+        <v>6600483</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2186,14 +2186,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132421599</v>
+        <v>132421617</v>
       </c>
       <c r="B15" t="n">
         <v>56811</v>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691727</v>
+        <v>691729</v>
       </c>
       <c r="R15" t="n">
-        <v>6600487</v>
+        <v>6600481</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2302,39 +2302,39 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132421617</v>
+        <v>132421705</v>
       </c>
       <c r="B16" t="n">
-        <v>56811</v>
+        <v>56830</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691729</v>
+        <v>691725</v>
       </c>
       <c r="R16" t="n">
-        <v>6600481</v>
+        <v>6600486</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2388,12 +2388,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132421589</v>
+        <v>132421641</v>
       </c>
       <c r="B20" t="n">
         <v>56811</v>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691725</v>
+        <v>691727</v>
       </c>
       <c r="R20" t="n">
-        <v>6600486</v>
+        <v>6600484</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2889,7 +2889,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132421641</v>
+        <v>132421662</v>
       </c>
       <c r="B21" t="n">
         <v>56811</v>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691727</v>
+        <v>691725</v>
       </c>
       <c r="R21" t="n">
-        <v>6600484</v>
+        <v>6600486</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2998,14 +2998,14 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132421688</v>
+        <v>132421604</v>
       </c>
       <c r="B22" t="n">
         <v>56811</v>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691717</v>
+        <v>691727</v>
       </c>
       <c r="R22" t="n">
-        <v>6600486</v>
+        <v>6600488</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132421604</v>
+        <v>132421673</v>
       </c>
       <c r="B23" t="n">
         <v>56811</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691727</v>
+        <v>691729</v>
       </c>
       <c r="R23" t="n">
         <v>6600488</v>
@@ -3230,14 +3230,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132421673</v>
+        <v>132421688</v>
       </c>
       <c r="B24" t="n">
         <v>56811</v>
@@ -3286,10 +3286,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691729</v>
+        <v>691717</v>
       </c>
       <c r="R24" t="n">
-        <v>6600488</v>
+        <v>6600486</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132421686</v>
+        <v>132421614</v>
       </c>
       <c r="B25" t="n">
         <v>56811</v>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691710</v>
+        <v>691728</v>
       </c>
       <c r="R25" t="n">
-        <v>6600483</v>
+        <v>6600482</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132421614</v>
+        <v>132421686</v>
       </c>
       <c r="B26" t="n">
         <v>56811</v>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691728</v>
+        <v>691710</v>
       </c>
       <c r="R26" t="n">
-        <v>6600482</v>
+        <v>6600483</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3933,7 +3933,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132421656</v>
+        <v>132421404</v>
       </c>
       <c r="B30" t="n">
         <v>56811</v>
@@ -3985,7 +3985,7 @@
         <v>691723</v>
       </c>
       <c r="R30" t="n">
-        <v>6600487</v>
+        <v>6600494</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4049,7 +4049,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132421404</v>
+        <v>132421656</v>
       </c>
       <c r="B31" t="n">
         <v>56811</v>
@@ -4101,7 +4101,7 @@
         <v>691723</v>
       </c>
       <c r="R31" t="n">
-        <v>6600494</v>
+        <v>6600487</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -3353,7 +3353,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132421614</v>
+        <v>132421686</v>
       </c>
       <c r="B25" t="n">
         <v>56811</v>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691728</v>
+        <v>691710</v>
       </c>
       <c r="R25" t="n">
-        <v>6600482</v>
+        <v>6600483</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3469,7 +3469,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132421686</v>
+        <v>132421614</v>
       </c>
       <c r="B26" t="n">
         <v>56811</v>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691710</v>
+        <v>691728</v>
       </c>
       <c r="R26" t="n">
-        <v>6600483</v>
+        <v>6600482</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132421630</v>
+        <v>132421821</v>
       </c>
       <c r="B3" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691727</v>
+        <v>691718</v>
       </c>
       <c r="R3" t="n">
-        <v>6600486</v>
+        <v>6600485</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,12 +880,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132421821</v>
+        <v>132421630</v>
       </c>
       <c r="B4" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691718</v>
+        <v>691727</v>
       </c>
       <c r="R4" t="n">
-        <v>6600485</v>
+        <v>6600486</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,12 +996,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1036,7 +1036,7 @@
         <v>132421639</v>
       </c>
       <c r="B5" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132421572</v>
+        <v>132421646</v>
       </c>
       <c r="B6" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691728</v>
+        <v>691724</v>
       </c>
       <c r="R6" t="n">
-        <v>6600492</v>
+        <v>6600486</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1268,7 +1268,7 @@
         <v>132421585</v>
       </c>
       <c r="B7" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>132421654</v>
       </c>
       <c r="B8" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132421646</v>
+        <v>132421572</v>
       </c>
       <c r="B9" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691724</v>
+        <v>691728</v>
       </c>
       <c r="R9" t="n">
-        <v>6600486</v>
+        <v>6600492</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1616,7 +1616,7 @@
         <v>132421680</v>
       </c>
       <c r="B10" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>132421678</v>
       </c>
       <c r="B11" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>132421615</v>
       </c>
       <c r="B12" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>132421599</v>
       </c>
       <c r="B13" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,7 +2080,7 @@
         <v>132421652</v>
       </c>
       <c r="B14" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>132421617</v>
       </c>
       <c r="B15" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>132421705</v>
       </c>
       <c r="B16" t="n">
-        <v>56830</v>
+        <v>56831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2428,7 +2428,7 @@
         <v>132421540</v>
       </c>
       <c r="B17" t="n">
-        <v>56825</v>
+        <v>56826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2534,17 +2534,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132421664</v>
+        <v>132421589</v>
       </c>
       <c r="B18" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691724</v>
+        <v>691725</v>
       </c>
       <c r="R18" t="n">
-        <v>6600489</v>
+        <v>6600486</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2657,10 +2657,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132421390</v>
+        <v>132421664</v>
       </c>
       <c r="B19" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691727</v>
+        <v>691724</v>
       </c>
       <c r="R19" t="n">
-        <v>6600492</v>
+        <v>6600489</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2773,10 +2773,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132421641</v>
+        <v>132421390</v>
       </c>
       <c r="B20" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>691727</v>
       </c>
       <c r="R20" t="n">
-        <v>6600484</v>
+        <v>6600492</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2889,10 +2889,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132421662</v>
+        <v>132421641</v>
       </c>
       <c r="B21" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691725</v>
+        <v>691727</v>
       </c>
       <c r="R21" t="n">
-        <v>6600486</v>
+        <v>6600484</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3008,7 +3008,7 @@
         <v>132421604</v>
       </c>
       <c r="B22" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>132421673</v>
       </c>
       <c r="B23" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>132421688</v>
       </c>
       <c r="B24" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3353,10 +3353,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132421686</v>
+        <v>132421614</v>
       </c>
       <c r="B25" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3402,10 +3402,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691710</v>
+        <v>691728</v>
       </c>
       <c r="R25" t="n">
-        <v>6600483</v>
+        <v>6600482</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3469,10 +3469,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132421614</v>
+        <v>132421686</v>
       </c>
       <c r="B26" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3518,10 +3518,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691728</v>
+        <v>691710</v>
       </c>
       <c r="R26" t="n">
-        <v>6600482</v>
+        <v>6600483</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3585,10 +3585,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132421388</v>
+        <v>132421613</v>
       </c>
       <c r="B27" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691727</v>
+        <v>691728</v>
       </c>
       <c r="R27" t="n">
-        <v>6600493</v>
+        <v>6600483</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3664,12 +3664,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3701,10 +3701,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132421613</v>
+        <v>132421388</v>
       </c>
       <c r="B28" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3750,10 +3750,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691728</v>
+        <v>691727</v>
       </c>
       <c r="R28" t="n">
-        <v>6600483</v>
+        <v>6600493</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3820,7 +3820,7 @@
         <v>132421406</v>
       </c>
       <c r="B29" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>132421404</v>
       </c>
       <c r="B30" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4052,7 +4052,7 @@
         <v>132421656</v>
       </c>
       <c r="B31" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>132421622</v>
       </c>
       <c r="B32" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>132421528</v>
       </c>
       <c r="B33" t="n">
-        <v>56830</v>
+        <v>56831</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>132421669</v>
       </c>
       <c r="B34" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>132421672</v>
       </c>
       <c r="B35" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>132421685</v>
       </c>
       <c r="B36" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>132421403</v>
       </c>
       <c r="B37" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>132421822</v>
       </c>
       <c r="B38" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4980,7 +4980,7 @@
         <v>132421684</v>
       </c>
       <c r="B39" t="n">
-        <v>56811</v>
+        <v>56812</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132421821</v>
+        <v>132421639</v>
       </c>
       <c r="B3" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691718</v>
+        <v>691726</v>
       </c>
       <c r="R3" t="n">
-        <v>6600485</v>
+        <v>6600484</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,12 +880,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132421630</v>
+        <v>132421821</v>
       </c>
       <c r="B4" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691727</v>
+        <v>691718</v>
       </c>
       <c r="R4" t="n">
-        <v>6600486</v>
+        <v>6600485</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,12 +996,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1033,10 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132421639</v>
+        <v>132421630</v>
       </c>
       <c r="B5" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691726</v>
+        <v>691727</v>
       </c>
       <c r="R5" t="n">
-        <v>6600484</v>
+        <v>6600486</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1149,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132421646</v>
+        <v>132421585</v>
       </c>
       <c r="B6" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691724</v>
+        <v>691726</v>
       </c>
       <c r="R6" t="n">
-        <v>6600486</v>
+        <v>6600487</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132421585</v>
+        <v>132421653</v>
       </c>
       <c r="B7" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691726</v>
+        <v>691723</v>
       </c>
       <c r="R7" t="n">
-        <v>6600487</v>
+        <v>6600486</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132421654</v>
+        <v>132421646</v>
       </c>
       <c r="B8" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691723</v>
+        <v>691724</v>
       </c>
       <c r="R8" t="n">
         <v>6600486</v>
@@ -1500,7 +1500,7 @@
         <v>132421572</v>
       </c>
       <c r="B9" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>132421680</v>
       </c>
       <c r="B10" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         <v>132421678</v>
       </c>
       <c r="B11" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>132421615</v>
       </c>
       <c r="B12" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132421599</v>
+        <v>132421617</v>
       </c>
       <c r="B13" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691727</v>
+        <v>691729</v>
       </c>
       <c r="R13" t="n">
-        <v>6600487</v>
+        <v>6600481</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132421652</v>
+        <v>132421599</v>
       </c>
       <c r="B14" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691724</v>
+        <v>691727</v>
       </c>
       <c r="R14" t="n">
-        <v>6600483</v>
+        <v>6600487</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2193,10 +2193,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132421617</v>
+        <v>132421652</v>
       </c>
       <c r="B15" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691729</v>
+        <v>691724</v>
       </c>
       <c r="R15" t="n">
-        <v>6600481</v>
+        <v>6600483</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2312,7 +2312,7 @@
         <v>132421705</v>
       </c>
       <c r="B16" t="n">
-        <v>56831</v>
+        <v>56835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2425,32 +2425,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132421540</v>
+        <v>132421641</v>
       </c>
       <c r="B17" t="n">
-        <v>56826</v>
+        <v>56816</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691726</v>
+        <v>691727</v>
       </c>
       <c r="R17" t="n">
         <v>6600484</v>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2544,7 +2544,7 @@
         <v>132421589</v>
       </c>
       <c r="B18" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>132421664</v>
       </c>
       <c r="B19" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>132421390</v>
       </c>
       <c r="B20" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2889,32 +2889,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132421641</v>
+        <v>132421540</v>
       </c>
       <c r="B21" t="n">
-        <v>56812</v>
+        <v>56830</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691727</v>
+        <v>691726</v>
       </c>
       <c r="R21" t="n">
         <v>6600484</v>
@@ -2968,12 +2968,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3008,7 +3008,7 @@
         <v>132421604</v>
       </c>
       <c r="B22" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>132421673</v>
       </c>
       <c r="B23" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>132421688</v>
       </c>
       <c r="B24" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>132421614</v>
       </c>
       <c r="B25" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
         <v>132421686</v>
       </c>
       <c r="B26" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>132421613</v>
       </c>
       <c r="B27" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>132421388</v>
       </c>
       <c r="B28" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>132421406</v>
       </c>
       <c r="B29" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3933,10 +3933,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132421404</v>
+        <v>132421656</v>
       </c>
       <c r="B30" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>691723</v>
       </c>
       <c r="R30" t="n">
-        <v>6600494</v>
+        <v>6600487</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4049,10 +4049,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132421656</v>
+        <v>132421404</v>
       </c>
       <c r="B31" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>691723</v>
       </c>
       <c r="R31" t="n">
-        <v>6600487</v>
+        <v>6600494</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4168,7 +4168,7 @@
         <v>132421622</v>
       </c>
       <c r="B32" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>132421528</v>
       </c>
       <c r="B33" t="n">
-        <v>56831</v>
+        <v>56835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>132421669</v>
       </c>
       <c r="B34" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4516,7 +4516,7 @@
         <v>132421672</v>
       </c>
       <c r="B35" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>132421685</v>
       </c>
       <c r="B36" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4748,7 +4748,7 @@
         <v>132421403</v>
       </c>
       <c r="B37" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>132421822</v>
       </c>
       <c r="B38" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>132421684</v>
       </c>
       <c r="B39" t="n">
-        <v>56812</v>
+        <v>56816</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132421639</v>
+        <v>132421821</v>
       </c>
       <c r="B3" t="n">
         <v>56816</v>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691726</v>
+        <v>691718</v>
       </c>
       <c r="R3" t="n">
-        <v>6600484</v>
+        <v>6600485</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,12 +880,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132421821</v>
+        <v>132421639</v>
       </c>
       <c r="B4" t="n">
         <v>56816</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691718</v>
+        <v>691726</v>
       </c>
       <c r="R4" t="n">
-        <v>6600485</v>
+        <v>6600484</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,12 +996,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132421653</v>
+        <v>132421654</v>
       </c>
       <c r="B7" t="n">
         <v>56816</v>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132421680</v>
+        <v>132421678</v>
       </c>
       <c r="B10" t="n">
         <v>56816</v>
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691724</v>
+        <v>691725</v>
       </c>
       <c r="R10" t="n">
         <v>6600488</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132421678</v>
+        <v>132421594</v>
       </c>
       <c r="B11" t="n">
         <v>56816</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691725</v>
+        <v>691724</v>
       </c>
       <c r="R11" t="n">
         <v>6600488</v>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132421615</v>
+        <v>132421599</v>
       </c>
       <c r="B12" t="n">
         <v>56816</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691729</v>
+        <v>691727</v>
       </c>
       <c r="R12" t="n">
-        <v>6600482</v>
+        <v>6600487</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132421617</v>
+        <v>132421652</v>
       </c>
       <c r="B13" t="n">
         <v>56816</v>
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691729</v>
+        <v>691724</v>
       </c>
       <c r="R13" t="n">
-        <v>6600481</v>
+        <v>6600483</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2077,7 +2077,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132421599</v>
+        <v>132421617</v>
       </c>
       <c r="B14" t="n">
         <v>56816</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691727</v>
+        <v>691729</v>
       </c>
       <c r="R14" t="n">
-        <v>6600487</v>
+        <v>6600481</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2193,32 +2193,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132421652</v>
+        <v>132421705</v>
       </c>
       <c r="B15" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691724</v>
+        <v>691725</v>
       </c>
       <c r="R15" t="n">
-        <v>6600483</v>
+        <v>6600486</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2309,32 +2309,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132421705</v>
+        <v>132421615</v>
       </c>
       <c r="B16" t="n">
-        <v>56835</v>
+        <v>56816</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691725</v>
+        <v>691729</v>
       </c>
       <c r="R16" t="n">
-        <v>6600486</v>
+        <v>6600482</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2388,12 +2388,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2425,32 +2425,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132421641</v>
+        <v>132421540</v>
       </c>
       <c r="B17" t="n">
-        <v>56816</v>
+        <v>56830</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691727</v>
+        <v>691726</v>
       </c>
       <c r="R17" t="n">
         <v>6600484</v>
@@ -2504,12 +2504,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2541,7 +2541,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132421589</v>
+        <v>132421641</v>
       </c>
       <c r="B18" t="n">
         <v>56816</v>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691725</v>
+        <v>691727</v>
       </c>
       <c r="R18" t="n">
-        <v>6600486</v>
+        <v>6600484</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132421664</v>
+        <v>132421589</v>
       </c>
       <c r="B19" t="n">
         <v>56816</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691724</v>
+        <v>691725</v>
       </c>
       <c r="R19" t="n">
-        <v>6600489</v>
+        <v>6600486</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132421390</v>
+        <v>132421664</v>
       </c>
       <c r="B20" t="n">
         <v>56816</v>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691727</v>
+        <v>691724</v>
       </c>
       <c r="R20" t="n">
-        <v>6600492</v>
+        <v>6600489</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2852,12 +2852,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2889,32 +2889,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132421540</v>
+        <v>132421390</v>
       </c>
       <c r="B21" t="n">
-        <v>56830</v>
+        <v>56816</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2938,10 +2938,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691726</v>
+        <v>691727</v>
       </c>
       <c r="R21" t="n">
-        <v>6600484</v>
+        <v>6600492</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3933,7 +3933,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132421656</v>
+        <v>132421404</v>
       </c>
       <c r="B30" t="n">
         <v>56816</v>
@@ -3985,7 +3985,7 @@
         <v>691723</v>
       </c>
       <c r="R30" t="n">
-        <v>6600487</v>
+        <v>6600494</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4049,7 +4049,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132421404</v>
+        <v>132421656</v>
       </c>
       <c r="B31" t="n">
         <v>56816</v>
@@ -4101,7 +4101,7 @@
         <v>691723</v>
       </c>
       <c r="R31" t="n">
-        <v>6600494</v>
+        <v>6600487</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132421821</v>
+        <v>132421630</v>
       </c>
       <c r="B3" t="n">
         <v>56816</v>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691718</v>
+        <v>691727</v>
       </c>
       <c r="R3" t="n">
-        <v>6600485</v>
+        <v>6600486</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,12 +880,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132421639</v>
+        <v>132421821</v>
       </c>
       <c r="B4" t="n">
         <v>56816</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691726</v>
+        <v>691718</v>
       </c>
       <c r="R4" t="n">
-        <v>6600484</v>
+        <v>6600485</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,12 +996,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,14 +1026,14 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132421630</v>
+        <v>132421639</v>
       </c>
       <c r="B5" t="n">
         <v>56816</v>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691727</v>
+        <v>691726</v>
       </c>
       <c r="R5" t="n">
-        <v>6600486</v>
+        <v>6600484</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132421585</v>
+        <v>132421654</v>
       </c>
       <c r="B6" t="n">
         <v>56816</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691726</v>
+        <v>691723</v>
       </c>
       <c r="R6" t="n">
-        <v>6600487</v>
+        <v>6600486</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132421654</v>
+        <v>132421646</v>
       </c>
       <c r="B7" t="n">
         <v>56816</v>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691723</v>
+        <v>691724</v>
       </c>
       <c r="R7" t="n">
         <v>6600486</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132421646</v>
+        <v>132421585</v>
       </c>
       <c r="B8" t="n">
         <v>56816</v>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691724</v>
+        <v>691726</v>
       </c>
       <c r="R8" t="n">
-        <v>6600486</v>
+        <v>6600487</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1613,7 +1613,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132421678</v>
+        <v>132421615</v>
       </c>
       <c r="B10" t="n">
         <v>56816</v>
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691725</v>
+        <v>691729</v>
       </c>
       <c r="R10" t="n">
-        <v>6600488</v>
+        <v>6600482</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132421599</v>
+        <v>132421617</v>
       </c>
       <c r="B12" t="n">
         <v>56816</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691727</v>
+        <v>691729</v>
       </c>
       <c r="R12" t="n">
-        <v>6600487</v>
+        <v>6600481</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1961,32 +1961,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132421652</v>
+        <v>132421705</v>
       </c>
       <c r="B13" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691724</v>
+        <v>691725</v>
       </c>
       <c r="R13" t="n">
-        <v>6600483</v>
+        <v>6600486</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2077,7 +2077,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132421617</v>
+        <v>132421678</v>
       </c>
       <c r="B14" t="n">
         <v>56816</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691729</v>
+        <v>691725</v>
       </c>
       <c r="R14" t="n">
-        <v>6600481</v>
+        <v>6600488</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2193,32 +2193,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132421705</v>
+        <v>132421599</v>
       </c>
       <c r="B15" t="n">
-        <v>56835</v>
+        <v>56816</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691725</v>
+        <v>691727</v>
       </c>
       <c r="R15" t="n">
-        <v>6600486</v>
+        <v>6600487</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2272,12 +2272,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2309,7 +2309,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132421615</v>
+        <v>132421652</v>
       </c>
       <c r="B16" t="n">
         <v>56816</v>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691729</v>
+        <v>691724</v>
       </c>
       <c r="R16" t="n">
-        <v>6600482</v>
+        <v>6600483</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132421641</v>
+        <v>132421589</v>
       </c>
       <c r="B18" t="n">
         <v>56816</v>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691727</v>
+        <v>691725</v>
       </c>
       <c r="R18" t="n">
-        <v>6600484</v>
+        <v>6600486</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2657,7 +2657,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132421589</v>
+        <v>132421390</v>
       </c>
       <c r="B19" t="n">
         <v>56816</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691725</v>
+        <v>691727</v>
       </c>
       <c r="R19" t="n">
-        <v>6600486</v>
+        <v>6600492</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2889,7 +2889,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132421390</v>
+        <v>132421641</v>
       </c>
       <c r="B21" t="n">
         <v>56816</v>
@@ -2941,7 +2941,7 @@
         <v>691727</v>
       </c>
       <c r="R21" t="n">
-        <v>6600492</v>
+        <v>6600484</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2968,12 +2968,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -4281,32 +4281,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132421528</v>
+        <v>132421669</v>
       </c>
       <c r="B33" t="n">
-        <v>56835</v>
+        <v>56816</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691727</v>
+        <v>691729</v>
       </c>
       <c r="R33" t="n">
-        <v>6600488</v>
+        <v>6600483</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4397,32 +4397,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132421669</v>
+        <v>132421528</v>
       </c>
       <c r="B34" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4446,10 +4446,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691729</v>
+        <v>691727</v>
       </c>
       <c r="R34" t="n">
-        <v>6600483</v>
+        <v>6600488</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -3933,7 +3933,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132421404</v>
+        <v>132421656</v>
       </c>
       <c r="B30" t="n">
         <v>56816</v>
@@ -3985,7 +3985,7 @@
         <v>691723</v>
       </c>
       <c r="R30" t="n">
-        <v>6600494</v>
+        <v>6600487</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4049,7 +4049,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132421656</v>
+        <v>132421404</v>
       </c>
       <c r="B31" t="n">
         <v>56816</v>
@@ -4101,7 +4101,7 @@
         <v>691723</v>
       </c>
       <c r="R31" t="n">
-        <v>6600487</v>
+        <v>6600494</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4281,32 +4281,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132421669</v>
+        <v>132421528</v>
       </c>
       <c r="B33" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691729</v>
+        <v>691727</v>
       </c>
       <c r="R33" t="n">
-        <v>6600483</v>
+        <v>6600488</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4397,32 +4397,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132421528</v>
+        <v>132421669</v>
       </c>
       <c r="B34" t="n">
-        <v>56835</v>
+        <v>56816</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4446,10 +4446,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691727</v>
+        <v>691729</v>
       </c>
       <c r="R34" t="n">
-        <v>6600488</v>
+        <v>6600483</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132421630</v>
+        <v>132421821</v>
       </c>
       <c r="B3" t="n">
         <v>56816</v>
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691727</v>
+        <v>691718</v>
       </c>
       <c r="R3" t="n">
-        <v>6600486</v>
+        <v>6600485</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,12 +880,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,7 +917,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132421821</v>
+        <v>132421630</v>
       </c>
       <c r="B4" t="n">
         <v>56816</v>
@@ -966,10 +966,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691718</v>
+        <v>691727</v>
       </c>
       <c r="R4" t="n">
-        <v>6600485</v>
+        <v>6600486</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,12 +996,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1149,7 +1149,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132421654</v>
+        <v>132421585</v>
       </c>
       <c r="B6" t="n">
         <v>56816</v>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691723</v>
+        <v>691726</v>
       </c>
       <c r="R6" t="n">
-        <v>6600486</v>
+        <v>6600487</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132421646</v>
+        <v>132421654</v>
       </c>
       <c r="B7" t="n">
         <v>56816</v>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691724</v>
+        <v>691723</v>
       </c>
       <c r="R7" t="n">
         <v>6600486</v>
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132421585</v>
+        <v>132421646</v>
       </c>
       <c r="B8" t="n">
         <v>56816</v>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691726</v>
+        <v>691724</v>
       </c>
       <c r="R8" t="n">
-        <v>6600487</v>
+        <v>6600486</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1613,32 +1613,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132421615</v>
+        <v>132421705</v>
       </c>
       <c r="B10" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1662,10 +1662,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691729</v>
+        <v>691725</v>
       </c>
       <c r="R10" t="n">
-        <v>6600482</v>
+        <v>6600486</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1729,7 +1729,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132421594</v>
+        <v>132421680</v>
       </c>
       <c r="B11" t="n">
         <v>56816</v>
@@ -1845,7 +1845,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132421617</v>
+        <v>132421678</v>
       </c>
       <c r="B12" t="n">
         <v>56816</v>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691729</v>
+        <v>691725</v>
       </c>
       <c r="R12" t="n">
-        <v>6600481</v>
+        <v>6600488</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1961,32 +1961,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132421705</v>
+        <v>132421615</v>
       </c>
       <c r="B13" t="n">
-        <v>56835</v>
+        <v>56816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2010,10 +2010,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691725</v>
+        <v>691729</v>
       </c>
       <c r="R13" t="n">
-        <v>6600486</v>
+        <v>6600482</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2040,12 +2040,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2077,7 +2077,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132421678</v>
+        <v>132421599</v>
       </c>
       <c r="B14" t="n">
         <v>56816</v>
@@ -2126,10 +2126,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691725</v>
+        <v>691727</v>
       </c>
       <c r="R14" t="n">
-        <v>6600488</v>
+        <v>6600487</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132421599</v>
+        <v>132421652</v>
       </c>
       <c r="B15" t="n">
         <v>56816</v>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691727</v>
+        <v>691724</v>
       </c>
       <c r="R15" t="n">
-        <v>6600487</v>
+        <v>6600483</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132421652</v>
+        <v>132421617</v>
       </c>
       <c r="B16" t="n">
         <v>56816</v>
@@ -2358,10 +2358,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691724</v>
+        <v>691729</v>
       </c>
       <c r="R16" t="n">
-        <v>6600483</v>
+        <v>6600481</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2541,7 +2541,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132421589</v>
+        <v>132421390</v>
       </c>
       <c r="B18" t="n">
         <v>56816</v>
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691725</v>
+        <v>691727</v>
       </c>
       <c r="R18" t="n">
-        <v>6600486</v>
+        <v>6600492</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2620,12 +2620,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2657,7 +2657,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132421390</v>
+        <v>132421589</v>
       </c>
       <c r="B19" t="n">
         <v>56816</v>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691727</v>
+        <v>691725</v>
       </c>
       <c r="R19" t="n">
-        <v>6600492</v>
+        <v>6600486</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2736,12 +2736,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3926,14 +3926,14 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132421656</v>
+        <v>132421404</v>
       </c>
       <c r="B30" t="n">
         <v>56816</v>
@@ -3985,7 +3985,7 @@
         <v>691723</v>
       </c>
       <c r="R30" t="n">
-        <v>6600487</v>
+        <v>6600494</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4042,14 +4042,14 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132421404</v>
+        <v>132421656</v>
       </c>
       <c r="B31" t="n">
         <v>56816</v>
@@ -4101,7 +4101,7 @@
         <v>691723</v>
       </c>
       <c r="R31" t="n">
-        <v>6600494</v>
+        <v>6600487</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Johan Allmér</t>
+          <t>Johan Allmér, Stina Hällholm</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Allmér, Stina Hällholm</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103385552</v>
+        <v>132421296</v>
       </c>
       <c r="B2" t="n">
-        <v>56521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103035</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,24 +708,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännbacken, Upl</t>
+          <t>Brännbacken Skeppsbol, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691694.0406630321</v>
+        <v>691726</v>
       </c>
       <c r="R2" t="n">
-        <v>6600507.944031614</v>
+        <v>6600495</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,27 +754,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Revirkartering</t>
+          <t>Fladdermusinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,37 +784,41 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stina Hällholm, Aron Norrby</t>
+          <t>Stina Hällholm, Johan Allmér</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132421821</v>
+        <v>132421301</v>
       </c>
       <c r="B3" t="n">
-        <v>56816</v>
+        <v>56849</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
@@ -846,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691718</v>
+        <v>691744</v>
       </c>
       <c r="R3" t="n">
-        <v>6600485</v>
+        <v>6600492</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,12 +870,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -913,30 +907,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132421639</v>
+        <v>132421537</v>
       </c>
       <c r="B4" t="n">
-        <v>56816</v>
+        <v>56849</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
@@ -958,10 +956,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691726</v>
+        <v>691733</v>
       </c>
       <c r="R4" t="n">
-        <v>6600484</v>
+        <v>6600493</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,12 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1025,30 +1023,34 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132421630</v>
+        <v>132421538</v>
       </c>
       <c r="B5" t="n">
-        <v>56816</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
@@ -1070,10 +1072,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691727</v>
+        <v>691733</v>
       </c>
       <c r="R5" t="n">
-        <v>6600486</v>
+        <v>6600491</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,12 +1102,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1137,30 +1139,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132421585</v>
+        <v>132421539</v>
       </c>
       <c r="B6" t="n">
-        <v>56816</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
@@ -1182,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691726</v>
+        <v>691731</v>
       </c>
       <c r="R6" t="n">
-        <v>6600487</v>
+        <v>6600493</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1249,30 +1255,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132421654</v>
+        <v>132421540</v>
       </c>
       <c r="B7" t="n">
-        <v>56816</v>
+        <v>56849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1294,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691723</v>
+        <v>691726</v>
       </c>
       <c r="R7" t="n">
-        <v>6600486</v>
+        <v>6600484</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,12 +1334,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1361,30 +1371,34 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132421646</v>
+        <v>132421543</v>
       </c>
       <c r="B8" t="n">
-        <v>56816</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
@@ -1406,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691724</v>
+        <v>691730</v>
       </c>
       <c r="R8" t="n">
-        <v>6600486</v>
+        <v>6600504</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1473,30 +1487,34 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132421572</v>
+        <v>132421544</v>
       </c>
       <c r="B9" t="n">
-        <v>56816</v>
+        <v>56849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
@@ -1518,10 +1536,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691728</v>
+        <v>691732</v>
       </c>
       <c r="R9" t="n">
-        <v>6600492</v>
+        <v>6600501</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,12 +1566,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1585,33 +1603,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132421680</v>
+        <v>132422726</v>
       </c>
       <c r="B10" t="n">
-        <v>56816</v>
+        <v>56849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1621,19 +1643,19 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>detektor med höghastighetsinspelning</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brännbacken Skeppsbol, Upl</t>
+          <t>Brännbacksvägen södra, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691724</v>
+        <v>691710</v>
       </c>
       <c r="R10" t="n">
-        <v>6600488</v>
+        <v>6600520</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,12 +1682,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1697,33 +1719,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132421678</v>
+        <v>132422728</v>
       </c>
       <c r="B11" t="n">
-        <v>56816</v>
+        <v>56842</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1733,19 +1759,19 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>detektor med höghastighetsinspelning</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Brännbacken Skeppsbol, Upl</t>
+          <t>Brännbacksvägen södra, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691725</v>
+        <v>691710</v>
       </c>
       <c r="R11" t="n">
-        <v>6600488</v>
+        <v>6600520</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1772,12 +1798,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1809,30 +1835,34 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132421615</v>
+        <v>132421528</v>
       </c>
       <c r="B12" t="n">
-        <v>56816</v>
+        <v>56854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1854,10 +1884,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691729</v>
+        <v>691727</v>
       </c>
       <c r="R12" t="n">
-        <v>6600482</v>
+        <v>6600488</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1921,30 +1951,34 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132421599</v>
+        <v>132421705</v>
       </c>
       <c r="B13" t="n">
-        <v>56816</v>
+        <v>56854</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>1</t>
@@ -1966,10 +2000,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691727</v>
+        <v>691725</v>
       </c>
       <c r="R13" t="n">
-        <v>6600487</v>
+        <v>6600486</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1996,12 +2030,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2033,33 +2067,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132421652</v>
+        <v>132422724</v>
       </c>
       <c r="B14" t="n">
-        <v>56816</v>
+        <v>56854</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cnephaeus nilssonii</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2069,19 +2107,19 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>detektor med höghastighetsinspelning</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brännbacken Skeppsbol, Upl</t>
+          <t>Brännbacksvägen södra, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691724</v>
+        <v>691710</v>
       </c>
       <c r="R14" t="n">
-        <v>6600483</v>
+        <v>6600520</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2108,12 +2146,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2145,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132421617</v>
+        <v>132421372</v>
       </c>
       <c r="B15" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2190,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691729</v>
+        <v>691740</v>
       </c>
       <c r="R15" t="n">
-        <v>6600481</v>
+        <v>6600487</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2220,12 +2258,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2257,34 +2295,30 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132421705</v>
+        <v>132421375</v>
       </c>
       <c r="B16" t="n">
-        <v>56837</v>
+        <v>56833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
@@ -2306,10 +2340,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691725</v>
+        <v>691741</v>
       </c>
       <c r="R16" t="n">
-        <v>6600486</v>
+        <v>6600488</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2336,12 +2370,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2373,34 +2407,30 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132421540</v>
+        <v>132421376</v>
       </c>
       <c r="B17" t="n">
-        <v>56832</v>
+        <v>56833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(Schreber, 1774)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>1</t>
@@ -2422,10 +2452,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691726</v>
+        <v>691736</v>
       </c>
       <c r="R17" t="n">
-        <v>6600484</v>
+        <v>6600491</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2489,10 +2519,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132421589</v>
+        <v>132421377</v>
       </c>
       <c r="B18" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2534,10 +2564,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691725</v>
+        <v>691733</v>
       </c>
       <c r="R18" t="n">
-        <v>6600486</v>
+        <v>6600494</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2564,12 +2594,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2601,10 +2631,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132421664</v>
+        <v>132421378</v>
       </c>
       <c r="B19" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691724</v>
+        <v>691727</v>
       </c>
       <c r="R19" t="n">
-        <v>6600489</v>
+        <v>6600496</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2676,12 +2706,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2713,10 +2743,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132421390</v>
+        <v>132421379</v>
       </c>
       <c r="B20" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2761,7 +2791,7 @@
         <v>691727</v>
       </c>
       <c r="R20" t="n">
-        <v>6600492</v>
+        <v>6600495</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2825,10 +2855,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132421641</v>
+        <v>132421382</v>
       </c>
       <c r="B21" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2870,10 +2900,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691727</v>
+        <v>691726</v>
       </c>
       <c r="R21" t="n">
-        <v>6600484</v>
+        <v>6600495</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2900,12 +2930,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2937,10 +2967,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132421688</v>
+        <v>132421383</v>
       </c>
       <c r="B22" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2982,10 +3012,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691717</v>
+        <v>691728</v>
       </c>
       <c r="R22" t="n">
-        <v>6600486</v>
+        <v>6600493</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3012,12 +3042,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3049,10 +3079,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132421604</v>
+        <v>132421384</v>
       </c>
       <c r="B23" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3097,7 +3127,7 @@
         <v>691727</v>
       </c>
       <c r="R23" t="n">
-        <v>6600488</v>
+        <v>6600494</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3124,12 +3154,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3161,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132421673</v>
+        <v>132421387</v>
       </c>
       <c r="B24" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,10 +3236,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691729</v>
+        <v>691727</v>
       </c>
       <c r="R24" t="n">
-        <v>6600488</v>
+        <v>6600493</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3236,12 +3266,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3273,10 +3303,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132421614</v>
+        <v>132421390</v>
       </c>
       <c r="B25" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3318,10 +3348,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691728</v>
+        <v>691727</v>
       </c>
       <c r="R25" t="n">
-        <v>6600482</v>
+        <v>6600492</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3348,12 +3378,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3385,10 +3415,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132421686</v>
+        <v>132421396</v>
       </c>
       <c r="B26" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3430,10 +3460,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691710</v>
+        <v>691726</v>
       </c>
       <c r="R26" t="n">
-        <v>6600483</v>
+        <v>6600496</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3460,12 +3490,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -3497,10 +3527,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132421613</v>
+        <v>132421399</v>
       </c>
       <c r="B27" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3542,10 +3572,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691728</v>
+        <v>691723</v>
       </c>
       <c r="R27" t="n">
-        <v>6600483</v>
+        <v>6600498</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3572,12 +3602,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3609,10 +3639,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132421388</v>
+        <v>132421401</v>
       </c>
       <c r="B28" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3654,10 +3684,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691727</v>
+        <v>691725</v>
       </c>
       <c r="R28" t="n">
-        <v>6600493</v>
+        <v>6600498</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3721,10 +3751,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132421406</v>
+        <v>132421402</v>
       </c>
       <c r="B29" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3766,10 +3796,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691722</v>
+        <v>691726</v>
       </c>
       <c r="R29" t="n">
-        <v>6600494</v>
+        <v>6600498</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3833,10 +3863,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132421404</v>
+        <v>132421403</v>
       </c>
       <c r="B30" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3881,7 +3911,7 @@
         <v>691723</v>
       </c>
       <c r="R30" t="n">
-        <v>6600494</v>
+        <v>6600495</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3945,10 +3975,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132421656</v>
+        <v>132421404</v>
       </c>
       <c r="B31" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3993,7 +4023,7 @@
         <v>691723</v>
       </c>
       <c r="R31" t="n">
-        <v>6600487</v>
+        <v>6600494</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4020,12 +4050,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4057,10 +4087,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132421622</v>
+        <v>132421406</v>
       </c>
       <c r="B32" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4102,10 +4132,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691728</v>
+        <v>691722</v>
       </c>
       <c r="R32" t="n">
-        <v>6600481</v>
+        <v>6600494</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4132,12 +4162,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4169,10 +4199,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132421669</v>
+        <v>132421407</v>
       </c>
       <c r="B33" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4214,10 +4244,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691729</v>
+        <v>691696</v>
       </c>
       <c r="R33" t="n">
-        <v>6600483</v>
+        <v>6600528</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4244,12 +4274,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
@@ -4281,34 +4311,30 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132421528</v>
+        <v>132421408</v>
       </c>
       <c r="B34" t="n">
-        <v>56837</v>
+        <v>56833</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>1</t>
@@ -4330,10 +4356,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691727</v>
+        <v>691695</v>
       </c>
       <c r="R34" t="n">
-        <v>6600488</v>
+        <v>6600529</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4360,12 +4386,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4397,10 +4423,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132421672</v>
+        <v>132421553</v>
       </c>
       <c r="B35" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,10 +4468,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691729</v>
+        <v>691744</v>
       </c>
       <c r="R35" t="n">
-        <v>6600484</v>
+        <v>6600489</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4472,12 +4498,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4509,10 +4535,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132421685</v>
+        <v>132421555</v>
       </c>
       <c r="B36" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,10 +4580,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691712</v>
+        <v>691744</v>
       </c>
       <c r="R36" t="n">
-        <v>6600483</v>
+        <v>6600488</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4584,12 +4610,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4621,10 +4647,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132421403</v>
+        <v>132421557</v>
       </c>
       <c r="B37" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,10 +4692,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691723</v>
+        <v>691739</v>
       </c>
       <c r="R37" t="n">
-        <v>6600495</v>
+        <v>6600487</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4733,10 +4759,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132421822</v>
+        <v>132421558</v>
       </c>
       <c r="B38" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,10 +4804,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691715</v>
+        <v>691733</v>
       </c>
       <c r="R38" t="n">
-        <v>6600484</v>
+        <v>6600491</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4808,12 +4834,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4845,10 +4871,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132421684</v>
+        <v>132421560</v>
       </c>
       <c r="B39" t="n">
-        <v>56816</v>
+        <v>56833</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,10 +4916,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691725</v>
+        <v>691733</v>
       </c>
       <c r="R39" t="n">
-        <v>6600492</v>
+        <v>6600493</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4920,12 +4946,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
@@ -4954,6 +4980,4278 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132421562</v>
+      </c>
+      <c r="B40" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>691731</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6600493</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>132421563</v>
+      </c>
+      <c r="B41" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>691731</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6600494</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132421564</v>
+      </c>
+      <c r="B42" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>691730</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6600494</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>132421565</v>
+      </c>
+      <c r="B43" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>691728</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6600492</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>132421567</v>
+      </c>
+      <c r="B44" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>691729</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6600493</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>132421584</v>
+      </c>
+      <c r="B45" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>691725</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6600488</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>132421585</v>
+      </c>
+      <c r="B46" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>691726</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6600487</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>132421586</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>691726</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6600484</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>132421588</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>691725</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6600486</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>132421592</v>
+      </c>
+      <c r="B49" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>691724</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6600488</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>132421597</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>691724</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6600489</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>132421598</v>
+      </c>
+      <c r="B51" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>691727</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6600487</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>132421603</v>
+      </c>
+      <c r="B52" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>691727</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6600488</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>132421607</v>
+      </c>
+      <c r="B53" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>691727</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6600486</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>132421610</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>691728</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6600483</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>132421612</v>
+      </c>
+      <c r="B55" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>691728</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6600482</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>132421615</v>
+      </c>
+      <c r="B56" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>691729</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6600482</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>132421617</v>
+      </c>
+      <c r="B57" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>691729</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6600481</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>132421621</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>691728</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6600481</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>132421631</v>
+      </c>
+      <c r="B59" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>691727</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6600484</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>132421645</v>
+      </c>
+      <c r="B60" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>691724</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6600486</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>132421651</v>
+      </c>
+      <c r="B61" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>691724</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6600483</v>
+      </c>
+      <c r="S61" t="n">
+        <v>25</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>132421653</v>
+      </c>
+      <c r="B62" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>691723</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6600486</v>
+      </c>
+      <c r="S62" t="n">
+        <v>25</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>132421655</v>
+      </c>
+      <c r="B63" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>691723</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6600487</v>
+      </c>
+      <c r="S63" t="n">
+        <v>25</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>132421669</v>
+      </c>
+      <c r="B64" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>691729</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6600483</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>132421672</v>
+      </c>
+      <c r="B65" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>691729</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6600484</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>132421673</v>
+      </c>
+      <c r="B66" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>691729</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6600488</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>132421684</v>
+      </c>
+      <c r="B67" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>691725</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6600492</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>132421685</v>
+      </c>
+      <c r="B68" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>691712</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6600483</v>
+      </c>
+      <c r="S68" t="n">
+        <v>25</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>132421686</v>
+      </c>
+      <c r="B69" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>691710</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6600483</v>
+      </c>
+      <c r="S69" t="n">
+        <v>25</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>132421688</v>
+      </c>
+      <c r="B70" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>691717</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6600486</v>
+      </c>
+      <c r="S70" t="n">
+        <v>25</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>132421821</v>
+      </c>
+      <c r="B71" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>691718</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6600485</v>
+      </c>
+      <c r="S71" t="n">
+        <v>25</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>132421822</v>
+      </c>
+      <c r="B72" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>691715</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6600484</v>
+      </c>
+      <c r="S72" t="n">
+        <v>25</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>132422730</v>
+      </c>
+      <c r="B73" t="n">
+        <v>56833</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Brännbacksvägen södra, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>691710</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6600520</v>
+      </c>
+      <c r="S73" t="n">
+        <v>25</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>132421292</v>
+      </c>
+      <c r="B74" t="n">
+        <v>56856</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>691727</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6600496</v>
+      </c>
+      <c r="S74" t="n">
+        <v>25</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>132421536</v>
+      </c>
+      <c r="B75" t="n">
+        <v>56856</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Brännbacken Skeppsbol, Upl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>691733</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6600491</v>
+      </c>
+      <c r="S75" t="n">
+        <v>25</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Johan Allmér</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>108924103</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Uggelbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>691731</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6600480</v>
+      </c>
+      <c r="S76" t="n">
+        <v>25</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Lark Davis</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Lark Davis</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>108924185</v>
+      </c>
+      <c r="B77" t="n">
+        <v>101897</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220075</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gullpudra</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Chrysosplenium alternifolium</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Uggelbo, Upl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>691737</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6600445</v>
+      </c>
+      <c r="S77" t="n">
+        <v>25</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2023-05-10</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Lark Davis</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Lark Davis</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22172-2022 artfynd.xlsx
+++ b/artfynd/A 22172-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AZ77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421296</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421301</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421537</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421538</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421539</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421540</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421543</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421544</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1716,6 +1761,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132422726</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1832,6 +1882,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132422728</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1948,6 +2003,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421528</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2064,6 +2124,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421705</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2180,6 +2245,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132422724</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2292,6 +2362,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421372</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2404,6 +2479,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421375</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2516,6 +2596,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421376</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2628,6 +2713,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421377</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2740,6 +2830,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421378</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2852,6 +2947,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421379</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2964,6 +3064,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421382</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3076,6 +3181,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421383</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3188,6 +3298,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421384</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3300,6 +3415,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421387</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3412,6 +3532,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421390</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3524,6 +3649,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421396</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3636,6 +3766,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421399</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3748,6 +3883,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421401</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3860,6 +4000,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421402</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3972,6 +4117,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421403</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4084,6 +4234,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421404</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4196,6 +4351,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421406</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4308,6 +4468,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421407</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4420,6 +4585,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421408</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4532,6 +4702,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421553</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4644,6 +4819,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421555</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4756,6 +4936,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421557</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4868,6 +5053,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421558</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4980,6 +5170,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421560</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5092,6 +5287,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421562</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5204,6 +5404,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421563</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5316,6 +5521,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421564</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5428,6 +5638,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421565</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5540,6 +5755,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421567</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5652,6 +5872,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421584</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5764,6 +5989,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421585</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5876,6 +6106,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421586</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5988,6 +6223,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421588</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6100,6 +6340,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421592</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6212,6 +6457,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421597</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6324,6 +6574,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421598</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6436,6 +6691,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421603</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6548,6 +6808,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421607</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6660,6 +6925,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421610</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6772,6 +7042,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421612</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6884,6 +7159,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421615</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6996,6 +7276,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421617</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7108,6 +7393,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421621</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7220,6 +7510,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421631</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7332,6 +7627,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421645</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7444,6 +7744,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421651</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7556,6 +7861,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421653</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7668,6 +7978,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421655</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7780,6 +8095,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421669</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7892,6 +8212,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421672</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8004,6 +8329,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421673</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8116,6 +8446,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421684</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8228,6 +8563,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421685</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8340,6 +8680,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421686</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8452,6 +8797,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421688</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8564,6 +8914,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421821</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8676,6 +9031,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421822</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8788,6 +9148,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132422730</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8904,6 +9269,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421292</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9020,6 +9390,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132421536</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9136,6 +9511,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108924103</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9252,8 +9632,91 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108924185</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>